--- a/public/TemplateExcel/ExamSchedule.xlsx
+++ b/public/TemplateExcel/ExamSchedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/38f9fe7ab19c9b08/Máy tính/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DoAn\EduAttend\fe\public\TemplateExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="8_{02D4C2EB-2EE8-49BC-8497-AC3F3F52631A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7573ED7-FDAD-46CA-B617-AA3D2529B709}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A13FA431-585B-4F94-A3A0-A540E0DDED11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DC5E073D-E881-4B6F-BA61-298051137D28}"/>
   </bookViews>
@@ -97,7 +97,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -105,16 +105,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -131,10 +148,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -464,47 +477,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="4">
         <v>46240</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="5">
         <v>0.39583333333333331</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="2">
         <v>90</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
         <v>6</v>
       </c>
+      <c r="G2" s="2"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
